--- a/CFD_models_results/iRonCub_Approximated_Measures.xlsx
+++ b/CFD_models_results/iRonCub_Approximated_Measures.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fdinatale\OneDrive - Fondazione Istituto Italiano Tecnologia\Desktop\Fabio\2.Lavoro\5.Fogli_di_Calcolo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fdinatale\OneDrive - Fondazione Istituto Italiano Tecnologia\Desktop\Fabio\2.Lavoro\4.Fogli_di_Calcolo\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,13 @@
   <sheets>
     <sheet name="Head" sheetId="1" r:id="rId1"/>
     <sheet name="Chest" sheetId="2" r:id="rId2"/>
-    <sheet name="Upper_Arm" sheetId="3" r:id="rId3"/>
-    <sheet name="Lower_Arm" sheetId="7" r:id="rId4"/>
-    <sheet name="Root_Link" sheetId="8" r:id="rId5"/>
-    <sheet name="Upper_Leg" sheetId="4" r:id="rId6"/>
-    <sheet name="Lower_Leg" sheetId="5" r:id="rId7"/>
-    <sheet name="Foot" sheetId="6" r:id="rId8"/>
+    <sheet name="Chest_With_JetPack" sheetId="9" r:id="rId3"/>
+    <sheet name="Upper_Arm" sheetId="3" r:id="rId4"/>
+    <sheet name="Lower_Arm" sheetId="7" r:id="rId5"/>
+    <sheet name="Root_Link" sheetId="8" r:id="rId6"/>
+    <sheet name="Upper_Leg" sheetId="4" r:id="rId7"/>
+    <sheet name="Lower_Leg" sheetId="5" r:id="rId8"/>
+    <sheet name="Foot" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="3">
   <si>
     <t>Base</t>
   </si>
@@ -513,6 +514,99 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
+      <xdr:colOff>220955</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>90170</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>365761</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>68273</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3025115" y="280670"/>
+          <a:ext cx="1973606" cy="2187903"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>82599</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>154333</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5928360" y="273099"/>
+          <a:ext cx="2857500" cy="2281534"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>405640</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>49311</xdr:rowOff>
@@ -601,7 +695,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -694,7 +788,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -787,7 +881,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -880,7 +974,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -973,7 +1067,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1695,7 +1789,7 @@
   <dimension ref="B1:O14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1735,11 +1829,11 @@
       <c r="O3" s="14"/>
     </row>
     <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="7">
-        <v>104.4</v>
-      </c>
-      <c r="C4" s="8">
-        <v>130</v>
+      <c r="B4" s="6">
+        <v>468.22</v>
+      </c>
+      <c r="C4" s="3">
+        <v>326.83</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="13"/>
@@ -1917,10 +2011,10 @@
     </row>
     <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="7">
-        <v>175.66</v>
+        <v>104.4</v>
       </c>
       <c r="C4" s="8">
-        <v>246.22</v>
+        <v>130</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="13"/>
@@ -2098,10 +2192,10 @@
     </row>
     <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="7">
-        <v>230.5</v>
+        <v>175.66</v>
       </c>
       <c r="C4" s="8">
-        <v>210.07</v>
+        <v>246.22</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="13"/>
@@ -2279,10 +2373,10 @@
     </row>
     <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="7">
-        <v>130</v>
+        <v>230.5</v>
       </c>
       <c r="C4" s="8">
-        <v>190</v>
+        <v>210.07</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="13"/>
@@ -2463,7 +2557,7 @@
         <v>130</v>
       </c>
       <c r="C4" s="8">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="13"/>
@@ -2600,6 +2694,187 @@
   <dimension ref="B1:O14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="11"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="11"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="12"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="14"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="14"/>
+    </row>
+    <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="7">
+        <v>130</v>
+      </c>
+      <c r="C4" s="8">
+        <v>200</v>
+      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="14"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="14"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="F5" s="12"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="14"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="14"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="F6" s="12"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="14"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="14"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="F7" s="12"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="14"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="14"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="F8" s="12"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="14"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="14"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="F9" s="12"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="14"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="14"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="F10" s="12"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="14"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="14"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="F11" s="12"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="14"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="14"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="F12" s="12"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="14"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="14"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="F13" s="12"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="14"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="14"/>
+    </row>
+    <row r="14" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F14" s="15"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="17"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F2:I14"/>
+    <mergeCell ref="K2:O14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:O14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
     <col min="2" max="2" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
   </cols>
@@ -2777,12 +3052,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2950,15 +3222,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{508CD969-BEC9-4820-B72F-1D3354FE47E3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02409E21-7239-4713-97D3-58FB089ACFDB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="be95f9c8-ee21-436a-9194-d67a31f0f9d0"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2982,17 +3265,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02409E21-7239-4713-97D3-58FB089ACFDB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{508CD969-BEC9-4820-B72F-1D3354FE47E3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be95f9c8-ee21-436a-9194-d67a31f0f9d0"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>